--- a/public/templates/giga-estimate.xlsx
+++ b/public/templates/giga-estimate.xlsx
@@ -5024,14 +5024,14 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>スモラの場合</t>
+    <t>ギガ賃貸の場合</t>
     <rPh sb="4" eb="6">
       <t>バアイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>スモ割</t>
+    <t>ギガ割</t>
     <rPh sb="2" eb="3">
       <t>ワリ</t>
     </rPh>
